--- a/pkg/parser/testfiles/barclaycard/Umsaetze_shortrows.xlsx
+++ b/pkg/parser/testfiles/barclaycard/Umsaetze_shortrows.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Transaktionsansicht</t>
   </si>
@@ -185,6 +185,15 @@
   </si>
   <si>
     <t>DetailB</t>
+  </si>
+  <si>
+    <t>PayPal Europe</t>
+  </si>
+  <si>
+    <t>XYZ  Rotterdam</t>
+  </si>
+  <si>
+    <t>Abc</t>
   </si>
 </sst>
 </file>
@@ -621,7 +630,7 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
         <v>35</v>
@@ -668,7 +677,7 @@
         <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
         <v>35</v>
@@ -720,7 +729,7 @@
         <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
